--- a/Preliminary Data/two forces (15 trials)(tapered and cylindrical)/Sigma Wrench Calcs.xlsx
+++ b/Preliminary Data/two forces (15 trials)(tapered and cylindrical)/Sigma Wrench Calcs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/two forces (15 trials)(tapered and cylindrical)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Bio-Inspired-Sensing/Preliminary Data/two forces (15 trials)(tapered and cylindrical)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_F25DC773A252ABDACC10483729DA651C5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A843C26-5DF2-495F-A736-E56955DB164D}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_F25DC773A252ABDACC10483729DA651C5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{542BF906-3B04-425B-9A0B-8DD467BE9469}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,6 +33,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -172,8 +194,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -183,8 +207,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -200,6 +223,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -465,40 +492,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>-9.8360656959638952E-4</v>
       </c>
@@ -517,8 +547,30 @@
       <c r="F3">
         <v>2.2138105950477785E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" cm="1">
+        <f t="array" ref="G3">SUMPRODUCT((A3:F3/$H$3:$M$3)^2)</f>
+        <v>4.290090112516054E-5</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>60</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
+      </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>-1.0536191984416954E-3</v>
       </c>
@@ -537,8 +589,12 @@
       <c r="F4">
         <v>-9.3957033574980434E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" cm="1">
+        <f t="array" ref="G4">SUMPRODUCT((A4:F4/$H$3:$M$3)^2)</f>
+        <v>1.9768758025270401E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2.2655842074553712E-3</v>
       </c>
@@ -557,8 +613,12 @@
       <c r="F5">
         <v>-0.1356491294248488</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" cm="1">
+        <f t="array" ref="G5">SUMPRODUCT((A5:F5/$H$3:$M$3)^2)</f>
+        <v>4.6722070812833572E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>-3.0652516333781986E-3</v>
       </c>
@@ -577,8 +637,12 @@
       <c r="F6">
         <v>5.8335136445672675E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" cm="1">
+        <f t="array" ref="G6">SUMPRODUCT((A6:F6/$H$3:$M$3)^2)</f>
+        <v>6.1317049435805502E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>-3.3054342025022692E-3</v>
       </c>
@@ -597,8 +661,12 @@
       <c r="F7">
         <v>8.3703172439121926E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" cm="1">
+        <f t="array" ref="G7">SUMPRODUCT((A7:F7/$H$3:$M$3)^2)</f>
+        <v>2.9751139077685844E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>-2.1031693480763863E-4</v>
       </c>
@@ -617,8 +685,12 @@
       <c r="F8">
         <v>2.8620525882628089E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" cm="1">
+        <f t="array" ref="G8">SUMPRODUCT((A8:F8/$H$3:$M$3)^2)</f>
+        <v>5.1989780794811018E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>-8.8192614933287408E-5</v>
       </c>
@@ -637,8 +709,12 @@
       <c r="F9">
         <v>8.2357309889192765E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" cm="1">
+        <f t="array" ref="G9">SUMPRODUCT((A9:F9/$H$3:$M$3)^2)</f>
+        <v>5.061983388022699E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>-6.2649394547785822E-4</v>
       </c>
@@ -657,8 +733,12 @@
       <c r="F10">
         <v>5.3695500075776781E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" cm="1">
+        <f t="array" ref="G10">SUMPRODUCT((A10:F10/$H$3:$M$3)^2)</f>
+        <v>2.0934149425004236E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>-8.6425604753312521E-4</v>
       </c>
@@ -677,8 +757,12 @@
       <c r="F11">
         <v>0.16824601495003511</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" cm="1">
+        <f t="array" ref="G11">SUMPRODUCT((A11:F11/$H$3:$M$3)^2)</f>
+        <v>1.0649468993701749E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5.1190470197925899E-4</v>
       </c>
@@ -697,8 +781,12 @@
       <c r="F12">
         <v>0.14363298813659309</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" cm="1">
+        <f t="array" ref="G12">SUMPRODUCT((A12:F12/$H$3:$M$3)^2)</f>
+        <v>4.816710015683433E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>-5.7422198841744466E-4</v>
       </c>
@@ -717,8 +805,12 @@
       <c r="F13">
         <v>5.652327756871145E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" cm="1">
+        <f t="array" ref="G13">SUMPRODUCT((A13:F13/$H$3:$M$3)^2)</f>
+        <v>1.633219460578665E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>-9.4429771523900179E-4</v>
       </c>
@@ -737,8 +829,12 @@
       <c r="F14">
         <v>-6.4146645615533626E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" cm="1">
+        <f t="array" ref="G14">SUMPRODUCT((A14:F14/$H$3:$M$3)^2)</f>
+        <v>2.90885011942491E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>-1.0358638511623617E-3</v>
       </c>
@@ -757,8 +853,12 @@
       <c r="F15">
         <v>0.14065421166017467</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" cm="1">
+        <f t="array" ref="G15">SUMPRODUCT((A15:F15/$H$3:$M$3)^2)</f>
+        <v>6.1933298724294917E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>-3.3381038754622741E-3</v>
       </c>
@@ -777,8 +877,12 @@
       <c r="F16">
         <v>0.15293837382443365</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" cm="1">
+        <f t="array" ref="G16">SUMPRODUCT((A16:F16/$H$3:$M$3)^2)</f>
+        <v>4.2388256726411588E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>-4.3059313707191507E-4</v>
       </c>
@@ -797,8 +901,12 @@
       <c r="F17">
         <v>-0.16968383775705329</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" cm="1">
+        <f t="array" ref="G17">SUMPRODUCT((A17:F17/$H$3:$M$3)^2)</f>
+        <v>1.8156459397631506E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>-9.7335534626927299E-4</v>
       </c>
@@ -817,8 +925,12 @@
       <c r="F18">
         <v>6.9846011870356717E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" cm="1">
+        <f t="array" ref="G18">SUMPRODUCT((A18:F18/$H$3:$M$3)^2)</f>
+        <v>3.3389804291761619E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>-1.1449491139260319E-3</v>
       </c>
@@ -837,8 +949,12 @@
       <c r="F19">
         <v>-3.5774078873262199E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" cm="1">
+        <f t="array" ref="G19">SUMPRODUCT((A19:F19/$H$3:$M$3)^2)</f>
+        <v>9.8062373685380474E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2.5008949260034953E-3</v>
       </c>
@@ -857,8 +973,12 @@
       <c r="F20">
         <v>-0.11738587778127019</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" cm="1">
+        <f t="array" ref="G20">SUMPRODUCT((A20:F20/$H$3:$M$3)^2)</f>
+        <v>1.3015233973402587E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>-1.8683481089326603E-3</v>
       </c>
@@ -877,8 +997,12 @@
       <c r="F21">
         <v>-1.8520203450577422E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" cm="1">
+        <f t="array" ref="G21">SUMPRODUCT((A21:F21/$H$3:$M$3)^2)</f>
+        <v>1.8764977810930138E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>-2.2763939325873448E-3</v>
       </c>
@@ -897,8 +1021,12 @@
       <c r="F22">
         <v>-5.542594283105548E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" cm="1">
+        <f t="array" ref="G22">SUMPRODUCT((A22:F22/$H$3:$M$3)^2)</f>
+        <v>1.1013354926673677E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2.1831674877726553E-5</v>
       </c>
@@ -917,8 +1045,12 @@
       <c r="F23">
         <v>5.8475902526015949E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23" cm="1">
+        <f t="array" ref="G23">SUMPRODUCT((A23:F23/$H$3:$M$3)^2)</f>
+        <v>8.7821525631795374E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>-1.5646171048963756E-3</v>
       </c>
@@ -937,8 +1069,12 @@
       <c r="F24">
         <v>7.2511475698173899E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" cm="1">
+        <f t="array" ref="G24">SUMPRODUCT((A24:F24/$H$3:$M$3)^2)</f>
+        <v>5.0965527331699038E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>-1.5927520343285433E-3</v>
       </c>
@@ -957,8 +1093,12 @@
       <c r="F25">
         <v>1.4258336355669421E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" cm="1">
+        <f t="array" ref="G25">SUMPRODUCT((A25:F25/$H$3:$M$3)^2)</f>
+        <v>8.0935906932355845E-5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>-2.9598900336361275E-3</v>
       </c>
@@ -977,8 +1117,12 @@
       <c r="F26">
         <v>0.11017490691826692</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" cm="1">
+        <f t="array" ref="G26">SUMPRODUCT((A26:F26/$H$3:$M$3)^2)</f>
+        <v>4.6266300652164118E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>-2.4981611006547549E-4</v>
       </c>
@@ -997,8 +1141,12 @@
       <c r="F27">
         <v>2.6205596248324969E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27" cm="1">
+        <f t="array" ref="G27">SUMPRODUCT((A27:F27/$H$3:$M$3)^2)</f>
+        <v>7.9811149442793385E-6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>-1.3586493767030817E-3</v>
       </c>
@@ -1017,8 +1165,12 @@
       <c r="F28">
         <v>8.753144830914783E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28" cm="1">
+        <f t="array" ref="G28">SUMPRODUCT((A28:F28/$H$3:$M$3)^2)</f>
+        <v>2.1896357196286438E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>-1.348653783107479E-3</v>
       </c>
@@ -1037,8 +1189,12 @@
       <c r="F29">
         <v>-0.12862977834001521</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29" cm="1">
+        <f t="array" ref="G29">SUMPRODUCT((A29:F29/$H$3:$M$3)^2)</f>
+        <v>9.3202751083588877E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>-2.0042647123105282E-3</v>
       </c>
@@ -1057,8 +1213,12 @@
       <c r="F30">
         <v>6.9869847527751716E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30" cm="1">
+        <f t="array" ref="G30">SUMPRODUCT((A30:F30/$H$3:$M$3)^2)</f>
+        <v>8.5168984041410851E-5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>-6.7532356240994455E-3</v>
       </c>
@@ -1077,31 +1237,65 @@
       <c r="F31">
         <v>5.6870872849057119E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
+      <c r="G31" cm="1">
+        <f t="array" ref="G31">SUMPRODUCT((A31:F31/$H$3:$M$3)^2)</f>
+        <v>4.2655692977501487E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <f>_xlfn.STDEV.S(A3:A31)</f>
         <v>1.7308713876288899E-3</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="2">
         <f t="shared" ref="B33:F33" si="0">_xlfn.STDEV.S(B3:B31)</f>
         <v>1.5982896731383811E-2</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="2">
         <f t="shared" si="0"/>
         <v>1.2150725520301957E-2</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="2">
         <f t="shared" si="0"/>
         <v>6.8383176976350671E-2</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="2">
         <f t="shared" si="0"/>
         <v>6.9384978806114564E-2</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="2">
         <f t="shared" si="0"/>
         <v>9.146823855200982E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f>AVERAGE(A3:A31)</f>
+        <v>-1.2177572925713784E-3</v>
+      </c>
+      <c r="B35">
+        <f t="shared" ref="B35:F35" si="1">AVERAGE(B3:B31)</f>
+        <v>-1.3714937512577662E-3</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="1"/>
+        <v>2.4964834858357391E-3</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="1"/>
+        <v>5.4927274088148563E-3</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="1"/>
+        <v>2.6226578856035652E-2</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="1"/>
+        <v>2.6002919675258813E-2</v>
+      </c>
+      <c r="G35" s="6">
+        <f>AVEDEV(G3:G31)</f>
+        <v>2.9661751125939403E-4</v>
       </c>
     </row>
   </sheetData>
